--- a/Team-Data/2013-14/3-18-2013-14.xlsx
+++ b/Team-Data/2013-14/3-18-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.47</v>
+        <v>0.462</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I2" t="n">
         <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
         <v>8.9</v>
@@ -715,31 +782,31 @@
         <v>25.3</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
         <v>8.4</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
         <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.8</v>
+        <v>101.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,16 +818,16 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
@@ -772,19 +839,19 @@
         <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -808,10 +875,10 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -942,22 +1009,22 @@
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -975,7 +1042,7 @@
         <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
@@ -1112,10 +1179,10 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1133,7 +1200,7 @@
         <v>11</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
@@ -1148,7 +1215,7 @@
         <v>29</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1157,7 +1224,7 @@
         <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1527,7 +1594,7 @@
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="n">
         <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
@@ -1589,10 +1656,10 @@
         <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
@@ -1610,22 +1677,22 @@
         <v>22.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R7" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
         <v>44.4</v>
       </c>
       <c r="U7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V7" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
@@ -1637,7 +1704,7 @@
         <v>5.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA7" t="n">
         <v>19.7</v>
@@ -1649,25 +1716,25 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -1676,10 +1743,10 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
@@ -1688,7 +1755,7 @@
         <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
@@ -1697,13 +1764,13 @@
         <v>15</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
@@ -1715,13 +1782,13 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB7" t="n">
         <v>24</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.623</v>
+        <v>0.618</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,10 +2384,10 @@
         <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L11" t="n">
         <v>9.199999999999999</v>
@@ -2338,46 +2405,46 @@
         <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
         <v>34.2</v>
       </c>
       <c r="T11" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
         <v>15.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="n">
         <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,16 +2456,16 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
@@ -2410,13 +2477,13 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2428,16 +2495,16 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2452,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2798,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2810,7 +2877,7 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3129,7 +3196,7 @@
         <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>26</v>
@@ -3171,13 +3238,13 @@
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3344,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.708</v>
+        <v>0.703</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3412,25 +3479,25 @@
         <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.507</v>
+        <v>0.508</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O17" t="n">
         <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.764</v>
       </c>
       <c r="R17" t="n">
         <v>7.4</v>
@@ -3442,7 +3509,7 @@
         <v>36.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V17" t="n">
         <v>14.9</v>
@@ -3460,16 +3527,16 @@
         <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="AC17" t="n">
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3505,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>17</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.191</v>
+        <v>0.194</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="J18" t="n">
-        <v>83</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.431</v>
@@ -3603,34 +3670,34 @@
         <v>20.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O18" t="n">
         <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R18" t="n">
         <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V18" t="n">
         <v>15</v>
       </c>
       <c r="W18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X18" t="n">
         <v>5</v>
@@ -3639,19 +3706,19 @@
         <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
         <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3672,7 +3739,7 @@
         <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3690,19 +3757,19 @@
         <v>23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>18</v>
@@ -3723,7 +3790,7 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3851,7 +3918,7 @@
         <v>11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3872,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4069,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4257,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
         <v>3</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>0.279</v>
+        <v>0.284</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4501,7 +4568,7 @@
         <v>37.1</v>
       </c>
       <c r="J23" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0.444</v>
@@ -4510,13 +4577,13 @@
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O23" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
         <v>20.8</v>
@@ -4528,10 +4595,10 @@
         <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>21</v>
@@ -4555,13 +4622,13 @@
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4618,7 +4685,7 @@
         <v>10</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>24</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
         <v>21</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4812,7 +4879,7 @@
         <v>26</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -4952,7 +5019,7 @@
         <v>4</v>
       </c>
       <c r="AM25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN25" t="n">
         <v>10</v>
@@ -4964,7 +5031,7 @@
         <v>7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
@@ -4979,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.647</v>
+        <v>0.642</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J26" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5056,28 +5123,28 @@
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O26" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="R26" t="n">
         <v>12.7</v>
       </c>
       <c r="S26" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="U26" t="n">
         <v>23.2</v>
@@ -5098,16 +5165,16 @@
         <v>19.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.6</v>
+        <v>107.4</v>
       </c>
       <c r="AC26" t="n">
         <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,22 +5186,22 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
@@ -5161,7 +5228,7 @@
         <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5176,10 +5243,10 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,7 +5296,7 @@
         <v>37</v>
       </c>
       <c r="J27" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
@@ -5244,10 +5311,10 @@
         <v>0.335</v>
       </c>
       <c r="O27" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="P27" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.766</v>
@@ -5256,16 +5323,16 @@
         <v>12.2</v>
       </c>
       <c r="S27" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T27" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="U27" t="n">
         <v>19</v>
       </c>
       <c r="V27" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W27" t="n">
         <v>7.3</v>
@@ -5274,22 +5341,22 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.4</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5337,7 +5404,7 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="n">
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
@@ -5605,25 +5672,25 @@
         <v>22.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R29" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U29" t="n">
         <v>21.4</v>
@@ -5632,7 +5699,7 @@
         <v>14.2</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5641,19 +5708,19 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5662,16 +5729,16 @@
         <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI29" t="n">
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -5683,7 +5750,7 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
@@ -5698,19 +5765,19 @@
         <v>13</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5874,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5907,7 +5974,7 @@
         <v>17</v>
       </c>
       <c r="BB30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31" t="n">
         <v>35</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.522</v>
+        <v>0.53</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K31" t="n">
         <v>0.455</v>
@@ -5966,19 +6033,19 @@
         <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N31" t="n">
         <v>0.386</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
@@ -5990,7 +6057,7 @@
         <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V31" t="n">
         <v>14.6</v>
@@ -6005,28 +6072,28 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -6053,10 +6120,10 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>25</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>26</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
@@ -6077,7 +6144,7 @@
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-18-2013-14</t>
+          <t>2014-03-18</t>
         </is>
       </c>
     </row>
